--- a/KakeiboAppBackEnd/src/main/resources/textfile/reactで覚えたこといくつか.xlsx
+++ b/KakeiboAppBackEnd/src/main/resources/textfile/reactで覚えたこといくつか.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjk037_\Desktop\git\KakeiboApp\KakeiboAppBackEnd\src\main\resources\textfile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655E03C3-3F34-4BA2-8E04-F850B1FA2006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8286798C-DF10-4501-8A40-A50D7EDD7B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7680" yWindow="285" windowWidth="15090" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="0" windowWidth="15090" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>useNavigate</t>
     <phoneticPr fontId="1"/>
@@ -127,6 +127,52 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一つのオブジェクトの上に複数のスイッチがあって、親への伝播を止めたいとき</t>
+    <rPh sb="0" eb="1">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オヤ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>デンパ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>target.stopPropagation();</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メインクラスを検出及びロードできませんでした：</t>
+    <rPh sb="7" eb="9">
+      <t>ケンシュツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このファイルを開いているからデータを更新できない</t>
+    <rPh sb="7" eb="8">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウシン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -465,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F19"/>
+  <dimension ref="A2:F26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
@@ -542,6 +588,26 @@
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
